--- a/exp_database/test_JACOS/RGB1_Morpho_Manual.xlsx
+++ b/exp_database/test_JACOS/RGB1_Morpho_Manual.xlsx
@@ -308,87 +308,87 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -651,19 +651,19 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="4" width="20.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="10.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="11.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="5" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="15.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="9.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="10.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="6" width="14.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="6" width="16.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="6" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="3" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="3" width="10.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="6" width="12.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="3" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="6" width="12.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="6" width="12.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="4" width="13.01"/>
   </cols>
   <sheetData>
